--- a/data/trans_orig/P80_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P80_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>629671</t>
+          <t>683557</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>623447</t>
+          <t>677106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>633189</t>
+          <t>687875</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>674320</t>
+          <t>731126</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>672134</t>
+          <t>727667</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>675210</t>
+          <t>732358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>99,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1303991</t>
+          <t>1414682</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1296993</t>
+          <t>1406815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1307738</t>
+          <t>1419012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>917</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>679</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1178468</t>
+          <t>1028800</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1166063</t>
+          <t>1015160</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1186552</t>
+          <t>1038125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>944332</t>
+          <t>1055216</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>936866</t>
+          <t>1047742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>948802</t>
+          <t>1060510</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2122800</t>
+          <t>2084016</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2110614</t>
+          <t>2067397</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2133372</t>
+          <t>2095602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -1520,67 +1520,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12736</t>
+          <t>23021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11713</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4799</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>12003</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13866</t>
+          <t>14934</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192188</t>
+          <t>1048183</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192188</t>
+          <t>1048183</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192188</t>
+          <t>1048183</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>955777</t>
+          <t>1068017</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>955777</t>
+          <t>1068017</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>955777</t>
+          <t>1068017</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2147965</t>
+          <t>2116200</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2147965</t>
+          <t>2116200</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2147965</t>
+          <t>2116200</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,17 +2089,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>685842</t>
+          <t>781677</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>668863</t>
+          <t>765756</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>694998</t>
+          <t>791354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>917738</t>
+          <t>794207</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>906702</t>
+          <t>784398</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>925085</t>
+          <t>800780</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1603578</t>
+          <t>1575883</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1585082</t>
+          <t>1557541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1616034</t>
+          <t>1587975</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31036</t>
+          <t>27961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>771</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>16823</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34344</t>
+          <t>31734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>16948</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14254</t>
+          <t>12243</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17871</t>
+          <t>21263</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>680</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>502</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>703750</t>
+          <t>802084</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>703750</t>
+          <t>802084</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>703750</t>
+          <t>802084</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>929785</t>
+          <t>808522</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>929785</t>
+          <t>808522</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>929785</t>
+          <t>808522</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1633534</t>
+          <t>1610605</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1633534</t>
+          <t>1610605</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1633534</t>
+          <t>1610605</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>897810</t>
+          <t>956814</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>883957</t>
+          <t>942276</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>907438</t>
+          <t>967182</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1069081</t>
+          <t>1091257</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1058078</t>
+          <t>1081044</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1077861</t>
+          <t>1099778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1966891</t>
+          <t>2048071</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1951263</t>
+          <t>2030133</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1980827</t>
+          <t>2061935</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>25288</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>18732</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36506</t>
+          <t>39306</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2997,67 +2997,67 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>6701</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3032</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>14595</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>5534</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24433</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -3110,59 +3110,59 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2265</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8650</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>9017</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,22 +3293,22 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>925825</t>
+          <t>988943</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>925825</t>
+          <t>988943</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>925825</t>
+          <t>988943</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1093687</t>
+          <t>1117670</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1093687</t>
+          <t>1117670</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1093687</t>
+          <t>1117670</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2019512</t>
+          <t>2106613</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2019512</t>
+          <t>2106613</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2019512</t>
+          <t>2106613</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3391790</t>
+          <t>3450847</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3368649</t>
+          <t>3424953</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3412246</t>
+          <t>3469150</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3605471</t>
+          <t>3671806</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3591344</t>
+          <t>3656141</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3618615</t>
+          <t>3683414</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6997261</t>
+          <t>7122653</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6970720</t>
+          <t>7092094</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7020570</t>
+          <t>7146288</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>37190</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>28895</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>57305</t>
+          <t>63289</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>54053</t>
+          <t>61038</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>39076</t>
+          <t>46894</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>73596</t>
+          <t>80997</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29751</t>
+          <t>38891</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14411</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23671</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>27062</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47070</t>
+          <t>56183</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,17 +3827,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20261</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>24471</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28699</t>
+          <t>31508</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
